--- a/output/pdf_financials_xlsx/LGD.xlsx
+++ b/output/pdf_financials_xlsx/LGD.xlsx
@@ -991,22 +991,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.709098</v>
+        <v>-6.709098</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7.877078</v>
+        <v>-6.927432</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>12.516994</v>
+        <v>-11.516974</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13.325767</v>
+        <v>-13.233213</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>12.845088</v>
+        <v>-11.163784</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>12.24672</v>
+        <v>-11.807604</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-21.387229</v>
@@ -1183,22 +1183,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6.709098</v>
+        <v>-6.709098</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>7.402255</v>
+        <v>-7.402255</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>12.016984</v>
+        <v>-12.016984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>13.27949</v>
+        <v>-13.27949</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>12.004436</v>
+        <v>-12.004436</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.027162</v>
+        <v>-12.027162</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-21.327841</v>
@@ -1300,22 +1300,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.709098</v>
+        <v>-6.709098</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7.402255</v>
+        <v>-7.402255</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>12.016984</v>
+        <v>-12.016984</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>13.27949</v>
+        <v>-13.27949</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.004436</v>
+        <v>-12.004436</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>12.027162</v>
+        <v>-12.027162</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-21.327841</v>
@@ -1429,37 +1429,31 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>95.844257</v>
+        <v>-95.844257</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>105.7465</v>
+        <v>-105.7465</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>133.522044</v>
+        <v>-133.522044</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>165.993625</v>
+        <v>-165.993625</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>200.073933</v>
+        <v>-200.073933</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>240.54324</v>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-240.54324</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>310.470019</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>326.34011</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>367.672353</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1474,22 +1468,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.388106</v>
+        <v>-7.03009</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.709302</v>
+        <v>-7.095208</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12.463667</v>
+        <v>-11.570301</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>13.263025</v>
+        <v>-13.295955</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.777088</v>
+        <v>-11.231784</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.184241</v>
+        <v>-11.870083</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-21.641033</v>
@@ -1552,22 +1546,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.388106</v>
+        <v>-7.03009</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.709302</v>
+        <v>-7.095208</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.463667</v>
+        <v>-11.570301</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>13.263025</v>
+        <v>-13.295955</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.831814</v>
+        <v>-11.177058</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>12.447122</v>
+        <v>-11.607202</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-21.101616</v>
@@ -1648,22 +1642,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>6.027907810485055</v>
+        <v>-6.854242668856222</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>3.994649194527057</v>
+        <v>-4.341504982124645</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.3472745696364044</v>
+        <v>-0.3497034318120626</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>6.544540605716365</v>
+        <v>-7.530170773637327</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.792790232813358</v>
+        <v>-1.85946276653587</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0.2776797312078156</v>
@@ -25010,22 +25004,22 @@
         </is>
       </c>
       <c r="E298" s="5" t="n">
-        <v>6.709098</v>
+        <v>-6.709098</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>7.402255</v>
+        <v>-7.402255</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>12.016984</v>
+        <v>-12.016984</v>
       </c>
       <c r="H298" s="5" t="n">
-        <v>13.27949</v>
+        <v>-13.27949</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>12.004436</v>
+        <v>-12.004436</v>
       </c>
       <c r="J298" s="5" t="n">
-        <v>12.027162</v>
+        <v>-12.027162</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -25324,16 +25318,16 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>11.461774</v>
+        <v>-11.461774</v>
       </c>
       <c r="H303" s="5" t="n">
-        <v>12.694734</v>
+        <v>-12.694734</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>13.174933</v>
+        <v>-13.174933</v>
       </c>
       <c r="J303" s="5" t="n">
-        <v>11.865275</v>
+        <v>-11.865275</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -25450,16 +25444,16 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>11.461774</v>
+        <v>-11.461774</v>
       </c>
       <c r="H305" s="5" t="n">
-        <v>12.694734</v>
+        <v>-12.694734</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>13.174933</v>
+        <v>-13.174933</v>
       </c>
       <c r="J305" s="5" t="n">
-        <v>11.865275</v>
+        <v>-11.865275</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -27372,10 +27366,10 @@
         </is>
       </c>
       <c r="E335" s="5" t="n">
-        <v>10.535641</v>
+        <v>-10.535641</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>13.41696</v>
+        <v>-13.41696</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -27574,10 +27568,10 @@
         </is>
       </c>
       <c r="E338" s="5" t="n">
-        <v>10.535641</v>
+        <v>-10.535641</v>
       </c>
       <c r="F338" s="5" t="n">
-        <v>13.41696</v>
+        <v>-13.41696</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LGD.xlsx
+++ b/output/pdf_financials_xlsx/LGD.xlsx
@@ -18332,7 +18332,11 @@
           <t>Purchase of reclamation deposits</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
         <v>-0.084522</v>
       </c>
@@ -18394,7 +18398,11 @@
           <t>Release of reclamation deposits (Note 9)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LGD.xlsx
+++ b/output/pdf_financials_xlsx/LGD.xlsx
@@ -1203,11 +1203,15 @@
       <c r="H20" s="3" t="n">
         <v>-21.327841</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>-20.807378</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-18.278988</v>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1243,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-2.208816</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-1.571153</v>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
@@ -2954,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.389345</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.359706</v>
       </c>
       <c r="K64" s="1" t="inlineStr">
         <is>
@@ -3050,36 +3054,34 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.765971</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.14424</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.08232399999999999</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.080022</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.122323</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.136332</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.6927219999999999</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.380453</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>352.965</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>1173.903</v>
       </c>
     </row>
     <row r="68">
@@ -3182,13 +3184,13 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.217654</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.278411</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.126601</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0</v>
@@ -3221,13 +3223,13 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.217654</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.278411</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.126601</v>
       </c>
       <c r="J71" s="3" t="n">
         <v>0</v>
@@ -3377,13 +3379,13 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>4.217654</v>
+        <v>4</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>1.066211</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.964401</v>
+        <v>0.8378</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>1.114507</v>
@@ -3582,15 +3584,13 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.01064207190190898</v>
+        <v>0.01691305926332854</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.001218318959279216</v>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007753963186949999</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.00416344216208935</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
@@ -8724,7 +8724,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13042,7 +13046,11 @@
           <t>Deferred tax expense (Note 12)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -15238,7 +15246,11 @@
           <t>Deferred tax expense (Note 11)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -16348,7 +16360,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -17428,7 +17444,11 @@
           <t>Deferred tax expense (Note 14)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -21964,7 +21984,11 @@
           <t>Net loss from discontinued operations (Notes 6)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
